--- a/pre-processing/data_cleaned/speaker.xlsx
+++ b/pre-processing/data_cleaned/speaker.xlsx
@@ -31,6 +31,9 @@
     <t>category</t>
   </si>
   <si>
+    <t>Loa bluetooth 5.3 PKCB 30W Super Bass TWS lên 60w TF Card/ Line in 3.5mm / AUX Stereo Surround, Loa Không Dây Nghe Nhạc Pin 3000Mah - Hàng Chính Hãng</t>
+  </si>
+  <si>
     <t>Loa Momo thông báo chuyển khoản - Tặng khay QRCode - Hàng chính hãng</t>
   </si>
   <si>
@@ -67,12 +70,12 @@
     <t>Loa hội nghị Bluetooth Anker PowerConf S500 - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Loa CROWN 5 đế có bluetooth ( Hàng Chính Hãng )</t>
-  </si>
-  <si>
     <t>Loa máy trợ giảng không dây Aporo T18 Plus 2.4G Wifi Bluetooth 5.0 Hàng Chính Hãng (Lựa chọn thêm Hộp bảo vệ Aporo)</t>
   </si>
   <si>
+    <t>Loa Bluetooth Karaoke  QIXI SK-2036 , Tặng Kèm 2 Micro Không Dây Cao Cấp , Hát Karaoke Nghe Nhạc Bass mạnh -Hàng Chính Hãng</t>
+  </si>
+  <si>
     <t>Máy Nghe Nhạc Bluetooth Thể Thao Ruizu X50 / X52 - Hàng Chính Hãng</t>
   </si>
   <si>
@@ -85,9 +88,6 @@
     <t>Loa vi tính loa gỗ công suất lớn dùng cho PC, Laptop, ĐT,Tivi - LEERFEI YST 3513 2.0 - NTH - Hàng Nhập Khẩu</t>
   </si>
   <si>
-    <t>Loa Bluetooth JBL Flip 6 - Hàng Chính Hãng</t>
-  </si>
-  <si>
     <t>Loa vi tính Q9 Sound Bar HD Led RGB cho máy tính, laptop, điện thoại, máy tính bảng hàng nhập khẩu</t>
   </si>
   <si>
@@ -97,15 +97,15 @@
     <t>Loa Bluetooth nghe nhạc không dây 100W công suất lớn Super Bass có cổng usb, thẻ nhớ, line 3.5mm pin 10400MAH sạc Type C Chip DSP TWS lên 200W cao cấp Hàng Chính Hãng PKCB</t>
   </si>
   <si>
-    <t>Loa Máy Tính Để Bàn, Âm Thanh Siêu Trầm, Dành Cho Học Online, Nghe Nhạc, Xem Phim - Hàng Chính Hãng</t>
-  </si>
-  <si>
     <t>Loa Bluetooth HXSJ V6 Bản Mở Rộng Hỗ Trợ Kết Nối Bluetooth 5.0, Thẻ Nhớ, USB, Công suất 2 loa 10W Nhiều Màu Sắc - Hàng chính hãng</t>
   </si>
   <si>
     <t>Máy trợ giảng không dây TAKSTAR E261W khoảng cách truyền 40M, công suất cao 25W -Tặng túi đựng máy trợ giảng - Hàng Chính Hãng</t>
   </si>
   <si>
+    <t>Loa Máy Tính Doron V-196 - Âm Thanh Siêu Trầm 4D, Bass Êm - Hàng Chính Hãng</t>
+  </si>
+  <si>
     <t>Combo Bộ Ba Loa Máy Tính Doron MC-D221 Super Bass , Âm Thanh Vòm 9D - Có Đèn Led - Hàng Nhập Khẩu</t>
   </si>
   <si>
@@ -148,7 +148,7 @@
     <t>Loa Vi Tính SoundMax A-130/2.0 6W</t>
   </si>
   <si>
-    <t>Loa bluetooth 5.3 PKCB 30W Super Bass TWS lên 60w TF Card/ Line in 3.5mm / AUX Stereo Surround, Loa Không Dây Nghe Nhạc Pin 3000Mah - Hàng Chính Hãng</t>
+    <t>Loa bluetooth 5.3 PKCB 20W Super Bass TWS lên 40w TF Card/ Line in 3.5mm / AUX Stereo Surround, Loa Không Dây Nghe Nhạc Pin 3000Mah - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Loa bluetooth LG xboom Grab - Hàng chính hãng</t>
@@ -166,9 +166,6 @@
     <t>Loa kéo công suất lớn bass 50 đơn Bossinon W-AM5579AK- CÔNG SUẤT 1.200W- Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Loa karaoke Dalton K210C công suất 850W, 2 bass 10 inches - HÀNG CHÍNH HÃNG ( BẢO HÀNH 12 THÁNG )</t>
-  </si>
-  <si>
     <t>MÁY TRỢ GIẢNG KHÔNG DÂY APORO T28 UHF CÓ CHỐNG NƯỚC IP67 CÔNG SUẤT LỚN HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
@@ -178,39 +175,45 @@
     <t>Loa kéo 5 tấc Bossinon W-AM5578K - _Kích thước: 510 (W) x 510 (D) x 840 (H)mm _Công suất: 1200Watts- Hàng chính Hãng</t>
   </si>
   <si>
+    <t>[NEW ARRIVAL] Loa Bluetooth Marshall Emberton III Portable - Hàng chính hãng</t>
+  </si>
+  <si>
     <t>Loa Logitech Bluetooth Ultimate Ears Everboom - Chống nước IP67 -  Hàng Chính Hãng</t>
   </si>
   <si>
+    <t>Loa Bluetooth JBL Go 4 JBLGO4 - Hàng chính hãng</t>
+  </si>
+  <si>
     <t>Loa Bluetooth iCore mini - Hàng chính hãng</t>
   </si>
   <si>
     <t>oa Máy trợ giảng Chính Hãng Aporo T18 2.4G Plus, T25 2.4G, Hàng Chính Hãng  (Bảo hành 12 tháng Quà Khuyến Mại)</t>
   </si>
   <si>
+    <t>Loa Bluetooth JBL Xtreme 4 - Hàng Chính Hãng</t>
+  </si>
+  <si>
     <t>Loa phóng thanh, Loa bán hàng có ghi âm, phát lại có cổng Usb - hàng chính hãng</t>
   </si>
   <si>
     <t>Loa Bluetooth Alpha Works W88 - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Loa Bluetooth Karaoke  QIXI SK-2036 , Tặng Kèm 2 Micro Không Dây Cao Cấp , Hát Karaoke Nghe Nhạc Bass mạnh -Hàng Chính Hãng</t>
-  </si>
-  <si>
     <t>LOA BLUETOOTH KARAOKE SUYOSD YS-230 KÈM 2 Micro không dây -Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Loa Bluetooth Marshall Acton III - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Loa vi tính cao cấp Logitech Z313 2.1 loa siêu trầm nhỏ gọn - Hàng Chính Hãng</t>
+    <t>Loa Bluetooth Marshall Woburn III - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Loa bluetooth hệ thống loa kép hỗ trợ TWS cho điện thoại laptop Hoco HC3 - hàng chính hãng</t>
   </si>
   <si>
     <t>Loa Bluetooth SoundMax R-800 - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Loa Bluetooth có đèn iCore B500 - Hàng Chính Hãng</t>
-  </si>
-  <si>
     <t>Loa Bluetooth PKCB Bản Mở Rộng, chip DSP, Hỗ Trợ Kết Nối Bluetooth, USB, Thẻ Nhớ,  dây 3.5mm 100W TWS Âm Thanh Sống Động - Hàng chính hãng</t>
   </si>
   <si>
@@ -229,13 +232,10 @@
     <t>Loa máy tính latop SoundMax A160 - Hàng chính hãng</t>
   </si>
   <si>
-    <t>Loa Máy Tính Doron V-196 - Âm Thanh Siêu Trầm 4D, Bass Êm - Hàng Chính Hãng</t>
-  </si>
-  <si>
     <t>Loa vi tính 2.0 SoundMax A140 Tổng Công Suất</t>
   </si>
   <si>
-    <t xml:space="preserve">Loa Bluetooth không dây Speaker nghe USB thẻ nhớ Cao cấp Hàng chính hãng </t>
+    <t>Loa Bluetooth  KLIPSCH HERITAGE GROOVE - Hàng chính hãng</t>
   </si>
   <si>
     <t>Loa Bluetooth IPx56 Plus Bản Mở Rộng, chống nước, âm thanh Bass cực mạnh. Hỗ Trợ Kết Nối Bluetooth 5.0, Micro Nhiều Màu Sắc - Hàng chính hãng</t>
@@ -256,7 +256,7 @@
     <t>Máy trợ giảng Unizone UZ-U2 - Máy trợ giảng không dây Hàn Quốc chính hãng mới nhất 2020</t>
   </si>
   <si>
-    <t>Loa Bluetooth Kiêm Pin Sạc Dự Phòng Zealot S1 – Hàng Nhập Khẩu</t>
+    <t>Loa bluetooth Karaoke Ruizu P88 hỗ trợ thẻ nhớ/USB/AUX/FM/jack 6.5mm - Tặng kèm micro karaoke (nhiều màu) Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Máy trợ giảng SHIDU SD-S358 - Hàng Chính Hãng</t>
@@ -268,34 +268,34 @@
     <t>Máy Nghe Nhạc MP3 Ruizu X02 8GB - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Loa bluetooth 5.3 PKCB 20W Super Bass TWS lên 40w TF Card/ Line in 3.5mm / AUX Stereo Surround, Loa Không Dây Nghe Nhạc Pin 3000Mah - Hàng Chính Hãng</t>
-  </si>
-  <si>
     <t>Loa Kéo Nanomax SK-12X5 ( Xám ) Bass 30cm 400w Karaoke Bluetooth Tặng Kèm 2 Mic Hát karaoke. Hàng chính hãng</t>
   </si>
   <si>
+    <t>Loa kéo tủ công suất lớn bass 40 đôi dùng bình, có đèn leb thương hiệu Bossinon N8119K- công suất 2.400w- Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Loa kéo hát karaoke xách tay Bossinon N2294K - Công suất 600W- Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Loa hát karaoke xách tay Bossinon K100B- Hàng chính Hãng</t>
+  </si>
+  <si>
     <t>Loa Bluetooth Anker Soundcore Select 4 Go A31X1 - Hàng chính hãng</t>
   </si>
   <si>
+    <t>Loa Bluetooth di động LG XBOOM GO XG2, Kháng nước IP67 - Hàng chính hãng</t>
+  </si>
+  <si>
     <t>Loa Bluetooth di động Energizer BTS081BK, bảo hành 24 tháng 1 đổi 1 - Hàng chính hãng</t>
   </si>
   <si>
-    <t>[NEW ARRIVAL] Loa Bluetooth Marshall Emberton III Portable - Hàng chính hãng</t>
-  </si>
-  <si>
     <t>Loa Bluetooth SoundMax  AT-100 - Hàng chính hãng</t>
   </si>
   <si>
     <t>Loa Bluetooth Logitech Ultimate Ears BOOM 4 - Chống nước, bụi - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Loa Bluetooth JBL Go 4 JBLGO4 - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Loa Bluetooth JBL Xtreme 4 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>12LW801 Củ loa Bass 12inch - 3 tấc Ferrite 500W 8Ω 18 Sound-HÀNG CHÍNH HÃNG</t>
+    <t>Loa Bluetooth JBL CLIP 5 JBLCLIP5 - Hàng chính hãng</t>
   </si>
   <si>
     <t>Loa Bluetooth S2025 kết nối không dây, âm thanh vượt trội đẳng cấp không gian-Hàng Chính Hãng</t>
@@ -307,9 +307,6 @@
     <t>Loa Kéo Nanomax SK-15D2 Xám Bass 40cm Công Suất 550w Karaoke Bluetooth Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Loa Bluetooth Harman Kardon Go Play 3  - Hàng Chính Hãng</t>
-  </si>
-  <si>
     <t>Loa Vi Tính Logitech Z407 Bluetooth, công suất 80W - Hàng chính hãng</t>
   </si>
   <si>
@@ -319,313 +316,319 @@
     <t>Loa Bluetooth Mini Sothing DW13 Vintage Retro Âm Thanh 3D, Decor Phòng Ngủ, Quà Tặng- Hàng chính hãng</t>
   </si>
   <si>
-    <t>Loa Bluetooth Sony SRS-XB100 - Hàng Chính Hãng</t>
+    <t>Loa Bluetooth Marshall Middleton Portable - Hàng Chính Hãng (Cream)</t>
+  </si>
+  <si>
+    <t>Edifier W820NB Plus - Tai Nghe Không Dây Bluetooth 5.2, ANC, Hi-Res Wireless, Màng Loa 40mm, Kết Nối Type-C, Hỗ Trợ Sạc Nhanh- Hàng chính hãng</t>
   </si>
   <si>
     <t>Loa Bluetooth Marshall Stanmore III - Hàng chính hãng</t>
   </si>
   <si>
-    <t>Loa Bluetooth Marshall Woburn III - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>images/speaker/product_277980303.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_277820438.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_277615987.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_277548884.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_277468981.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_277369759.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276582252.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276566181.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276386509.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276075466.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_275513834.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_275406083.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_275262949.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_274704359.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_252963851.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_252390163.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_196201409.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_191320811.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_188565088.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_171232872.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_164285225.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_160946349.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_153544569.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_127695415.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_127600345.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_117916066.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_108379905.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_95469367.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_88191430.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_82874789.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_82861299.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_80959641.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_77712221.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_76062253.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_73204703.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_57900120.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_35278834.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_13331940.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_6610413.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_104180.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_278149617.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_278067024.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_277771239.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_277582223.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_277581685.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_277421606.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276856800.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276253446.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276253314.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276251942.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_275855621.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_275467638.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_275254778.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_274943200.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_274046847.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_273084814.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_273054021.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_241639907.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_210138061.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_184077032.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_176167334.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_172369953.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_165345530.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_165025828.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_152521511.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_145717791.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_123926245.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_117987260.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_95866327.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_75301142.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_66758390.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_58393093.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_57523356.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_55508641.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_50322624.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_48576455.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_47099726.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_21430781.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_17539156.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_2013189.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_278149668.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_277521161.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276747066.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276280160.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276075423.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_276046012.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_275855728.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_275761136.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_275130480.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_274408482.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_274165805.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_273959250.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_273602049.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_273328383.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_272286025.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_271966725.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_271829222.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_271515346.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_241638318.jpg</t>
-  </si>
-  <si>
-    <t>images/speaker/product_241635069.jpg</t>
+    <t>Loa Bluetooth Divoom DiToo Pro, bảo hành 12 tháng 1 đổi 1 - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>images/speaker/278149617.png</t>
+  </si>
+  <si>
+    <t>images/speaker/277980303.png</t>
+  </si>
+  <si>
+    <t>images/speaker/277820438.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/277615987.png</t>
+  </si>
+  <si>
+    <t>images/speaker/277548884.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/277468981.png</t>
+  </si>
+  <si>
+    <t>images/speaker/277369759.png</t>
+  </si>
+  <si>
+    <t>images/speaker/276582252.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/276566181.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/276386509.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/276075466.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/275513834.png</t>
+  </si>
+  <si>
+    <t>images/speaker/275406083.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/274704359.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/273084814.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/252963851.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/252390163.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/196201409.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/191320811.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/171232872.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/164285225.png</t>
+  </si>
+  <si>
+    <t>images/speaker/160946349.png</t>
+  </si>
+  <si>
+    <t>images/speaker/127695415.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/127600345.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/117987260.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/117916066.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/108379905.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/95469367.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/88191430.png</t>
+  </si>
+  <si>
+    <t>images/speaker/82874789.png</t>
+  </si>
+  <si>
+    <t>images/speaker/82861299.png</t>
+  </si>
+  <si>
+    <t>images/speaker/80959641.png</t>
+  </si>
+  <si>
+    <t>images/speaker/77712221.png</t>
+  </si>
+  <si>
+    <t>images/speaker/76062253.png</t>
+  </si>
+  <si>
+    <t>images/speaker/73204703.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/57900120.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/35278834.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/13331940.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/6610413.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/104180.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/278149668.png</t>
+  </si>
+  <si>
+    <t>images/speaker/278067024.jpeg</t>
+  </si>
+  <si>
+    <t>images/speaker/277771239.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/277582223.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/277581685.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/277421606.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/276253446.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/276253314.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/276251942.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/276075423.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/275855621.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/275761136.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/275467638.png</t>
+  </si>
+  <si>
+    <t>images/speaker/275254778.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/275130480.png</t>
+  </si>
+  <si>
+    <t>images/speaker/274943200.jpeg</t>
+  </si>
+  <si>
+    <t>images/speaker/274046847.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/273054021.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/241639907.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/241635069.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/196854332.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/184077032.png</t>
+  </si>
+  <si>
+    <t>images/speaker/172369953.png</t>
+  </si>
+  <si>
+    <t>images/speaker/165345530.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/165025828.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/152521511.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/145717791.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/123926245.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/95866327.png</t>
+  </si>
+  <si>
+    <t>images/speaker/73653415.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/66758390.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/58393093.png</t>
+  </si>
+  <si>
+    <t>images/speaker/57523356.png</t>
+  </si>
+  <si>
+    <t>images/speaker/55508641.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/50322624.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/48576455.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/43851316.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/21430781.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/17539156.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/2013189.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/277521161.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/277421637.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/277420934.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/277327377.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/276747066.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/276292343.png</t>
+  </si>
+  <si>
+    <t>images/speaker/276280160.png</t>
+  </si>
+  <si>
+    <t>images/speaker/276046012.png</t>
+  </si>
+  <si>
+    <t>images/speaker/275855728.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/275543974.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/274165805.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/273959250.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/273602049.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/272286025.png</t>
+  </si>
+  <si>
+    <t>images/speaker/271966725.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/271829222.png</t>
+  </si>
+  <si>
+    <t>images/speaker/270214387.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/263256595.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/241638318.jpg</t>
+  </si>
+  <si>
+    <t>images/speaker/200817773.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e2/6d/f3/a4d4cab4832ad57cc0c85ee92a36b08f.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/82/71/46/f7df65cf5d97510dff1fec414610edfc.png</t>
@@ -658,18 +661,18 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/f1/2e/ed/8fe4edc4a67abf0ac2ef2aeb87bc3aab.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/67/aa/6b/7f2b935840624971dfbd626660edc66b.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/15/b0/cd/e40487b513bacfb1f280ba4e3edf9c01.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/2b/27/af/4523d339fd00437117b277e3d9ccb2f6.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/63/5f/51/93bb2369808b60ff5336cb7c65bb0c61.jpg</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/83/19/53/aca4c2b4f56e00b3d073918b2d9926fa.jpg</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/aa/44/db/3efe0d42e1a1fe9e434febdee93c5124.jpg</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/d1/12/1a/2f550c77ffce011eff2dc85327896306.jpg</t>
   </si>
   <si>
@@ -682,9 +685,6 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/23/ea/1c/ebce0794ababe54445ed6512e1de5ddb.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/58/50/8f/036b824c27d115608719f7bfe3a69dd4.jpg</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/8c/97/ec20d0a3e3a6c8ddb0befa8dcfd682c4.jpg</t>
   </si>
   <si>
@@ -694,15 +694,15 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/36/f5/c5/5a9d7f3c9c33940c5a9d74948ca61a3a.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/54/3f/73/0a05db6a772e5b7ea54060949482b2b9.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8a/89/33/9a062c76cacb992f4caaf632e0328eee.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e6/57/5a/d8151030de78ac15a026907a9a86dddc.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/05/b9/95/da3ede58bcd8d0556f3b1800a3ff342c.jpg</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0e/d1/ee/53f6046bf6dea3a962012f752d679134.jpg</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/4a/59/62/ee44eda734cddd9c8ab959fee71b193e.jpg</t>
   </si>
   <si>
@@ -748,7 +748,7 @@
     <t>https://salt.tikicdn.com/cache/280x280/media/catalog/product/a/1/a1301_1.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e2/6d/f3/a4d4cab4832ad57cc0c85ee92a36b08f.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4e/ae/eb/c6b4280801140832c7bbd7a7c886f451.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/31/28/77/2587ef3dae8c3aa997753a72b73abe03.jpeg</t>
@@ -766,9 +766,6 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/53/a2/08/4f321920e08c28fa85ac45135906871f.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/63/8d/8f/148eceabb190aeb9124d7adefa32e967.jpg</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/d0/93/77/dc03bbcf2e351eed632da89a6256e986.jpg</t>
   </si>
   <si>
@@ -778,39 +775,45 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/b3/8f/11/52b6b1a6e279c0fe706191ad28f2dea5.jpg</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0a/a3/eb/cc5756b3acc619c0ec6194d8d393dd62.jpg</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/2c/30/05/1dcfebb38150c2477c71db6423f6704f.jpg</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/01/3d/6f/5bd28a932f6142ad2dc67501212ce17a.jpg</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/79/22/59/82d6179545f64ec16342dcecad8d251f.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/f9/71/7c/1d408941370d1b781efa8302801bfbb5.jpg</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/84/3c/8a/0eeb030957b6eb401a54461e01a8eb3d.png</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/4f/60/16/e745b03f6bb85cf2c723c303447e653d.jpeg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/f4/20/9e/44c3280f221bf38dc46d7c4a14014c88.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/aa/44/db/3efe0d42e1a1fe9e434febdee93c5124.jpg</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/b6/8e/8f/c09fdaa1f3835ea67a281eda20f6d952.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/24/d6/c9/d6a4308749e746113d8895208183866d.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ae/91/8f/da146d4bd995ba29eea1af24a7d4bc7e.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/51/ec/17/5f5af5171e5b276b0aafb36e02c96149.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/15/7a/ef/424cc29bd6b08488a7fb95cf75868917.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/e1/bb/25/6c763d6fe5cf89a21d54032b18d158b4.PNG</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/81/c2/c2/1b6103d5dfcdacb81832e15b723a84d0.png</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/e4/e5/c1/4684a13cbc1f69f41e7581b41c0be5b3.png</t>
   </si>
   <si>
@@ -829,13 +832,10 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/2d/a5/95/bc5840dc1bbf7d717c067089b9a4a53e.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0e/d1/ee/53f6046bf6dea3a962012f752d679134.jpg</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/85/e2/e4/fd13ceb7f2e584a754bb3635d9c619e8.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9d/03/1b/6411a9d17b163c8f40e31547fd3aa77d.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ce/a3/14/cacb6a758c2518a8265f418abdb241be.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/1e/f5/7c/3ac79b78b48ac50309c28b00c0a2159a.jpg</t>
@@ -856,7 +856,7 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/a0/2c/d9/7ef61760de3f8acfc2359a68f76a1399.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/61/84/69/68ce542f043bcd9eec7af2427f4b3f93.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5f/4c/86/b196325aecfaa58f92568ba9d6c18020.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/a1/33/8a/e99d2cb1a2acf4bd4161188143d3ddb0.jpg</t>
@@ -868,34 +868,34 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/60/a1/3e/980edbcd9df066f5d6a4dd28e8759bbd.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4e/ae/eb/c6b4280801140832c7bbd7a7c886f451.png</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/4c/0e/16/256140f14845bbd0043c25b416409546.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0b/2b/72/aeccf4038fc189c6a55f98d4ecb40367.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9e/bf/37/00708cfaf555c835589cc1780edc7e7c.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9c/4a/4a/580de951fe35f7120638957daae16d96.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/73/c5/5e/0ce5616d4ae87efbf6a13d0c8f60061a.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0c/c9/c9/fd94ba09ff3a10550f42278d0377ee05.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/39/df/a8/f37d734f0d9ce6d0f45ca25e0e2f7c2b.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/29/c8/88/672676a6876a999b490aeb9ff1a4d2f4.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0a/a3/eb/cc5756b3acc619c0ec6194d8d393dd62.jpg</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/15/66/99/24495a61cc5adee6633a71ab376291e2.PNG</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/60/63/0f/1f466960d49010f990dac10986b4396b.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/01/3d/6f/5bd28a932f6142ad2dc67501212ce17a.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/84/3c/8a/0eeb030957b6eb401a54461e01a8eb3d.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/da/17/ff/a5d985db539810b089b6f8837f9e465a.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ca/d3/0c/c8b4b98e8ebfdb85e99a44d2fcf23e75.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/72/ef/fb/51597e709a5bfa7d35042f3cbd0883d2.jpg</t>
@@ -907,9 +907,6 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/97/a7/88/28357b633fd65e46d91711916432d019.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/06/3e/cb/55c0a3a5bc68f1094a16ec06a71209f7.jpg</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/82/64/36/68cf6b5918670c2827d3ddfe83a7c583.png</t>
   </si>
   <si>
@@ -919,13 +916,16 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/b5/15/84/ca4d8e7f99b81b49247c4c70e25a1e28.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/20/7a/b2/f5d6e605e4bc1deb9253b7bd96c5b46f.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1e/2e/25/5ee58bd1679065097fc39b4ba155cbaa.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/63/74/20/8ec0fe6a1ec6e142997ce101e5d95d13.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/bf/82/cd/3ceffdaf188510a10307d789bfe6ad5f.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/51/ec/17/5f5af5171e5b276b0aafb36e02c96149.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5d/ca/dd/da9e32f120549712954a4c3cd7c939c0.png</t>
   </si>
   <si>
     <t>Thiết Bị Số - Phụ Kiện Số</t>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>277980303</v>
+        <v>278149617</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>277820438</v>
+        <v>277980303</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -1355,7 +1355,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>277615987</v>
+        <v>277820438</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>277548884</v>
+        <v>277615987</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>277468981</v>
+        <v>277548884</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>277369759</v>
+        <v>277468981</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>276582252</v>
+        <v>277369759</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>276566181</v>
+        <v>276582252</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -1457,7 +1457,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>276386509</v>
+        <v>276566181</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>276075466</v>
+        <v>276386509</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>275513834</v>
+        <v>276075466</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>275406083</v>
+        <v>275513834</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>275262949</v>
+        <v>275406083</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>252963851</v>
+        <v>273084814</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>252390163</v>
+        <v>252963851</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>196201409</v>
+        <v>252390163</v>
       </c>
       <c r="B18" t="s">
         <v>21</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>191320811</v>
+        <v>196201409</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -1627,7 +1627,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>188565088</v>
+        <v>191320811</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>153544569</v>
+        <v>127695415</v>
       </c>
       <c r="B24" t="s">
         <v>27</v>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>127695415</v>
+        <v>127600345</v>
       </c>
       <c r="B25" t="s">
         <v>28</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>127600345</v>
+        <v>117987260</v>
       </c>
       <c r="B26" t="s">
         <v>29</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>278149617</v>
+        <v>278149668</v>
       </c>
       <c r="B42" t="s">
         <v>44</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>276856800</v>
+        <v>276253446</v>
       </c>
       <c r="B48" t="s">
         <v>50</v>
@@ -2120,7 +2120,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>276253446</v>
+        <v>276253314</v>
       </c>
       <c r="B49" t="s">
         <v>51</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>276253314</v>
+        <v>276251942</v>
       </c>
       <c r="B50" t="s">
         <v>52</v>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>276251942</v>
+        <v>276075423</v>
       </c>
       <c r="B51" t="s">
         <v>53</v>
@@ -2188,7 +2188,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>275467638</v>
+        <v>275761136</v>
       </c>
       <c r="B53" t="s">
         <v>55</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>275254778</v>
+        <v>275467638</v>
       </c>
       <c r="B54" t="s">
         <v>56</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>274943200</v>
+        <v>275254778</v>
       </c>
       <c r="B55" t="s">
         <v>57</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>274046847</v>
+        <v>275130480</v>
       </c>
       <c r="B56" t="s">
         <v>58</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>273084814</v>
+        <v>274943200</v>
       </c>
       <c r="B57" t="s">
         <v>59</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>273054021</v>
+        <v>274046847</v>
       </c>
       <c r="B58" t="s">
         <v>60</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>241639907</v>
+        <v>273054021</v>
       </c>
       <c r="B59" t="s">
         <v>61</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>210138061</v>
+        <v>241639907</v>
       </c>
       <c r="B60" t="s">
         <v>62</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>184077032</v>
+        <v>241635069</v>
       </c>
       <c r="B61" t="s">
         <v>63</v>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>176167334</v>
+        <v>196854332</v>
       </c>
       <c r="B62" t="s">
         <v>64</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>172369953</v>
+        <v>184077032</v>
       </c>
       <c r="B63" t="s">
         <v>65</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>165345530</v>
+        <v>172369953</v>
       </c>
       <c r="B64" t="s">
         <v>66</v>
@@ -2392,7 +2392,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>165025828</v>
+        <v>165345530</v>
       </c>
       <c r="B65" t="s">
         <v>67</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>152521511</v>
+        <v>165025828</v>
       </c>
       <c r="B66" t="s">
         <v>68</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>145717791</v>
+        <v>152521511</v>
       </c>
       <c r="B67" t="s">
         <v>69</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>123926245</v>
+        <v>145717791</v>
       </c>
       <c r="B68" t="s">
         <v>70</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>117987260</v>
+        <v>123926245</v>
       </c>
       <c r="B69" t="s">
         <v>71</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>75301142</v>
+        <v>73653415</v>
       </c>
       <c r="B71" t="s">
         <v>73</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>47099726</v>
+        <v>43851316</v>
       </c>
       <c r="B78" t="s">
         <v>80</v>
@@ -2681,7 +2681,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>278149668</v>
+        <v>277521161</v>
       </c>
       <c r="B82" t="s">
         <v>84</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>277521161</v>
+        <v>277421637</v>
       </c>
       <c r="B83" t="s">
         <v>85</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>276747066</v>
+        <v>277420934</v>
       </c>
       <c r="B84" t="s">
         <v>86</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>276280160</v>
+        <v>277327377</v>
       </c>
       <c r="B85" t="s">
         <v>87</v>
@@ -2749,7 +2749,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>276075423</v>
+        <v>276747066</v>
       </c>
       <c r="B86" t="s">
         <v>88</v>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>276046012</v>
+        <v>276292343</v>
       </c>
       <c r="B87" t="s">
         <v>89</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>275855728</v>
+        <v>276280160</v>
       </c>
       <c r="B88" t="s">
         <v>90</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>275761136</v>
+        <v>276046012</v>
       </c>
       <c r="B89" t="s">
         <v>91</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>275130480</v>
+        <v>275855728</v>
       </c>
       <c r="B90" t="s">
         <v>92</v>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>274408482</v>
+        <v>275543974</v>
       </c>
       <c r="B91" t="s">
         <v>93</v>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>273328383</v>
+        <v>272286025</v>
       </c>
       <c r="B95" t="s">
         <v>97</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>272286025</v>
+        <v>271966725</v>
       </c>
       <c r="B96" t="s">
         <v>98</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>271966725</v>
+        <v>271829222</v>
       </c>
       <c r="B97" t="s">
         <v>99</v>
@@ -2953,7 +2953,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>271829222</v>
+        <v>270214387</v>
       </c>
       <c r="B98" t="s">
         <v>100</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>271515346</v>
+        <v>263256595</v>
       </c>
       <c r="B99" t="s">
         <v>101</v>
@@ -3004,7 +3004,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>241635069</v>
+        <v>200817773</v>
       </c>
       <c r="B101" t="s">
         <v>103</v>
